--- a/webapp/fixtures/test_declarations.xlsx
+++ b/webapp/fixtures/test_declarations.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,86 +425,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>POTLDG</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>IMPDCLNUM</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>DTELDG</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CMPTAXNUM</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CMPBRN</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CMPNME</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>CMPNMEENG</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TRFCLS</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CTYOGN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CIFVALTHB</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>GDSDSC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>GDSDSCTH</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>WGT</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>WGTUNT</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>QTY</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>QTYUNT</t>
         </is>
@@ -501,60 +513,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0690700001</t>
+          <t>0630107595</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20260701</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0105558000011</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D2" t="n">
+        <v>115539003046</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>บริษัท เอเชีย อิเล็กทรอนิกส์ จำกัด</t>
+          <t>บริษัท ซีเอสนันเฟอร์รัส เซ็นเตอร์ จำกัด</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asia Electronics Co., Ltd.</t>
+          <t>CS.NON-FERROUS CENTER CO.,LTD.</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8542390090</v>
+        <v>72202010</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>44500</v>
+        <v>3053689.68</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>MEMORY INTEGRATED CIRCUIT DDR4 8GB</t>
+          <t>COLD ROLLED STAINLESS STEEL SUS304 2H SLIT EDGE IN COIL SUS304 2H 0.25MMX126MMXCOIL</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ไอซีความจำ DDR4 8GB</t>
+          <t>ผลิตภัณฑ์แผ่นรีดทำด้วยเหล็กกล้าไม่เป็นสนิม รีดเย็นกว้างน้อยกว่า 600 มม.</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>12.5</v>
+        <v>17312</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -562,71 +570,67 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>500</v>
+        <v>17.312</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>TNE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0690700002</t>
+          <t>0630107595</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20260702</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0105558000011</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D3" t="n">
+        <v>115539003046</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>บริษัท เอเชีย อิเล็กทรอนิกส์ จำกัด</t>
+          <t>บริษัท ซีเอสนันเฟอร์รัส เซ็นเตอร์ จำกัด</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asia Electronics Co., Ltd.</t>
+          <t>CS.NON-FERROUS CENTER CO.,LTD.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8542390090</v>
+        <v>72202010</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>46200</v>
+        <v>353640.97</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>MEMORY INTEGRATED CIRCUIT DDR4 16GB</t>
+          <t>COLD ROLLED STAINLESS STEEL SUS304 2H SLIT EDGE IN COIL SUS304 2H 0.30MMX126MMXCOIL</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ไอซีความจำ DDR4 16GB</t>
+          <t>ผลิตภัณฑ์แผ่นรีดทำด้วยเหล็กกล้าไม่เป็นสนิม รีดเย็นกว้างน้อยกว่า 600 มม.</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>2040</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -634,50 +638,46 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>480</v>
+        <v>2.04</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>TNE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0690700003</t>
+          <t>0630107602</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20260703</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0105558000011</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D4" t="n">
+        <v>107536000773</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>บริษัท เอเชีย อิเล็กทรอนิกส์ จำกัด</t>
+          <t>บริษัท ฮานา ไมโครอิเล็คโทรนิคส จำกัด (มหาชน)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asia Electronics Co., Ltd.</t>
+          <t>HANA MICROELECTRONICS PUBLIC COMPANY LIMITED.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8542390090</v>
+        <v>39235000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -685,20 +685,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1200</v>
+        <v>581773.97</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MEMORY INTEGRATED CIRCUIT DDR4 8GB</t>
+          <t>HO19019818@CHARGER 2.1,BOTTOM ENCLOSURE</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ไอซีความจำ DDR4 8GB</t>
+          <t>ฝาครอบชิ้นงาน</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -706,71 +706,67 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>500</v>
+        <v>2100</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>C62</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0690700004</t>
+          <t>0630107602</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20260704</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0105561000022</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D5" t="n">
+        <v>107536000773</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>บริษัท ไทยเซมิคอนดักเตอร์ จำกัด</t>
+          <t>บริษัท ฮานา ไมโครอิเล็คโทรนิคส จำกัด (มหาชน)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thai Semiconductor Co., Ltd.</t>
+          <t>HANA MICROELECTRONICS PUBLIC COMPANY LIMITED.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8542390010</v>
+        <v>39235000</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>38900</v>
+        <v>428894.24</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PROCESSING CONTROL INTEGRATED CIRCUIT</t>
+          <t>HO19019818@CHARGER 2.0,PRINTED LID</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ไอซีควบคุมการประมวลผล</t>
+          <t>ฝาครอบชิ้นงาน</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -778,71 +774,67 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>400</v>
+        <v>2100</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>C62</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0690700005</t>
+          <t>0630107602</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20260705</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0105561000022</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D6" t="n">
+        <v>107536000773</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>บริษัท ไทยเซมิคอนดักเตอร์ จำกัด</t>
+          <t>บริษัท ฮานา ไมโครอิเล็คโทรนิคส จำกัด (มหาชน)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thai Semiconductor Co., Ltd.</t>
+          <t>HANA MICROELECTRONICS PUBLIC COMPANY LIMITED.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8542390010</v>
+        <v>39235000</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>40200</v>
+        <v>94870.38</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PROCESSING CONTROL INTEGRATED CIRCUIT 32BIT</t>
+          <t>HO19019818@MAGNET,N52</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ไอซีควบคุมการประมวลผล 32บิต</t>
+          <t>ฝาครอบชิ้นงาน</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -850,71 +842,67 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>410</v>
+        <v>8000</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>C62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0690700006</t>
+          <t>0630107621</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20260706</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0105561000022</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D7" t="n">
+        <v>105506002610</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>บริษัท ไทยเซมิคอนดักเตอร์ จำกัด</t>
+          <t>บริษัท เอ็นเอชเค สปริง (ประเทศไทย) จำกัด (สาขา 3)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thai Semiconductor Co., Ltd.</t>
+          <t>NHK SPRING (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8542390010</v>
+        <v>73202011</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39500</v>
+        <v>42873.53</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>PROCESSING CONTROL INTEGRATED CIRCUIT 16BIT</t>
+          <t>SPRING REAR 02H1-44201</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ไอซีควบคุมการประมวลผล 16บิต</t>
+          <t>สปริงขด</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>10.2</v>
+        <v>315</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -922,71 +910,67 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>405</v>
+        <v>192</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>C62</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0690700007</t>
+          <t>0630107621</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20260707</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0105561000022</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D8" t="n">
+        <v>105506002610</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>บริษัท ไทยเซมิคอนดักเตอร์ จำกัด</t>
+          <t>บริษัท เอ็นเอชเค สปริง (ประเทศไทย) จำกัด (สาขา 3)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thai Semiconductor Co., Ltd.</t>
+          <t>NHK SPRING (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>8542390010</v>
+        <v>73202011</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>900</v>
+        <v>45381.77</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PROCESSING CONTROL INTEGRATED CIRCUIT</t>
+          <t>SPRING REAR 52441-TVL-T910-M2</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ไอซีควบคุมการประมวลผล</t>
+          <t>สปริงขด</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>9.800000000000001</v>
+        <v>315</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -994,50 +978,46 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>400</v>
+        <v>192</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>C62</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0690700008</t>
+          <t>0630107621</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20260708</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0105563000033</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D9" t="n">
+        <v>105506002610</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>บริษัท โมบายเทค อิมปอร์ต จำกัด</t>
+          <t>บริษัท เอ็นเอชเค สปริง (ประเทศไทย) จำกัด (สาขา 3)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MobileTech Import Co., Ltd.</t>
+          <t>NHK SPRING (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8517120010</v>
+        <v>73202011</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1045,20 +1025,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>15000</v>
+        <v>449151.23</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>MOBILE PHONE CHARGER ADAPTER 20W USB-C</t>
+          <t>SPRING REAR 52441-TWD-T010-M2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>เครื่องชาร์จโทรศัพท์มือถือ 20W USB-C</t>
+          <t>สปริงขด</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>3150</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1066,50 +1046,46 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1000</v>
+        <v>1920</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>C62</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0690700009</t>
+          <t>0630107621</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20260709</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0105563000033</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D10" t="n">
+        <v>105506002610</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>บริษัท โมบายเทค อิมปอร์ต จำกัด</t>
+          <t>บริษัท เอ็นเอชเค สปริง (ประเทศไทย) จำกัด (สาขา 3)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MobileTech Import Co., Ltd.</t>
+          <t>NHK SPRING (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8517120010</v>
+        <v>73202011</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1117,20 +1093,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>15800</v>
+        <v>359320.98</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>MOBILE PHONE CHARGER ADAPTER 20W USB-C FAST CHARGE</t>
+          <t>SPRING REAR 52441-TWD-T110-M2</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>เครื่องชาร์จโทรศัพท์มือถือ 20W USB-C ชาร์จเร็ว</t>
+          <t>สปริงขด</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>2519</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1138,71 +1114,67 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1050</v>
+        <v>1536</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>C62</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0690700010</t>
+          <t>0630107624</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20260710</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0105563000033</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D11" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>บริษัท โมบายเทค อิมปอร์ต จำกัด</t>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MobileTech Import Co., Ltd.</t>
+          <t>MAHAJAK KYODO CO., LTD.</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8517120010</v>
+        <v>72139190</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14700</v>
+        <v>348708.88</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>MOBILE PHONE CHARGER ADAPTER 18W USB-A</t>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  ELCH2S  9.00MM</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>เครื่องชาร์จโทรศัพท์มือถือ 18W USB-A</t>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมน้อยกว่า 14 มม.เหล็กไม่เจือ</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>24.5</v>
+        <v>7714</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1210,71 +1182,67 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>980</v>
+        <v>7.714</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>TNE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0690700011</t>
+          <t>0630107624</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20260711</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0105563000033</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D12" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>บริษัท โมบายเทค อิมปอร์ต จำกัด</t>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MobileTech Import Co., Ltd.</t>
+          <t>MAHAJAK KYODO CO., LTD.</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8517120010</v>
+        <v>72139990</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>600</v>
+        <v>70210.49000000001</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>MOBILE PHONE CHARGER ADAPTER 20W USB-C</t>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  S45C JIS G4051 17.00MM</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>เครื่องชาร์จโทรศัพท์มือถือ 20W USB-C</t>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>24</v>
+        <v>2016</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1282,71 +1250,67 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>950</v>
+        <v>2.016</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>TNE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0690700012</t>
+          <t>0630107624</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20260712</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0105565000044</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D13" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>บริษัท สมาร์ทโฟน แอคเซสซอรี่ จำกัด</t>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Smartphone Accessory Co., Ltd.</t>
+          <t>MAHAJAK KYODO CO., LTD.</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8517120090</v>
+        <v>72139990</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>28000</v>
+        <v>135614.91</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SMARTPHONE CASE PROTECTIVE COVER SILICONE</t>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  S45C JIS G4051 19.00MM</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>เคสโทรศัพท์มือถือซิลิโคนกันกระแทก</t>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>18</v>
+        <v>3894</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1354,71 +1318,67 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>2000</v>
+        <v>3.894</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>TNE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0690700013</t>
+          <t>0630107624</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20260713</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0105565000044</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D14" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>บริษัท สมาร์ทโฟน แอคเซสซอรี่ จำกัด</t>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Smartphone Accessory Co., Ltd.</t>
+          <t>MAHAJAK KYODO CO., LTD.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8517120090</v>
+        <v>72132000</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>27500</v>
+        <v>69444.31</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SMARTPHONE CASE PROTECTIVE COVER SILICONE CLEAR</t>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  KFS103 JIS G4804 11.50MM</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>เคสโทรศัพท์มือถือซิลิโคนใส</t>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ขดมาเป็นม้วนเหล็กตัดง่าย เหล็กไม่เจือ</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>17.5</v>
+        <v>1994</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1426,71 +1386,67 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1950</v>
+        <v>1.994</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>TNE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0690700014</t>
+          <t>0630107624</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20260714</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0105565000044</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D15" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>บริษัท สมาร์ทโฟน แอคเซสซอรี่ จำกัด</t>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Smartphone Accessory Co., Ltd.</t>
+          <t>MAHAJAK KYODO CO., LTD.</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8517120090</v>
+        <v>72132000</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29200</v>
+        <v>59588.51</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SMARTPHONE CASE PROTECTIVE COVER LEATHER</t>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  KFS103 JIS G4804 27.00MM</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>เคสโทรศัพท์มือถือหนัง</t>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ขดมาเป็นม้วนเหล็กตัดง่าย เหล็กไม่เจือ</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>18.2</v>
+        <v>1711</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1498,71 +1454,67 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2010</v>
+        <v>1.711</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>TNE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0690700015</t>
+          <t>0630107624</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20260715</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0105567000055</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D16" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>บริษัท สยาม การ์เมนท์ อิมปอร์ต จำกัด</t>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Siam Garment Import Co., Ltd.</t>
+          <t>MAHAJAK KYODO CO., LTD.</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6109100010</v>
+        <v>72279000</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>52000</v>
+        <v>80376.78999999999</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>MEN'S COTTON T-SHIRT ROUND NECK</t>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  SCM415H JIS G4052 12.70MM</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>เสื้อยืดคอกลมผู้ชาย ผ้าฝ้าย</t>
+          <t>เหล็กเส้นรีดร้อนขดมาเป็นม้วนทำด้วยเหล็กกล้าเจือ</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>180</v>
+        <v>1994</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1570,71 +1522,67 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>3000</v>
+        <v>1.994</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>TNE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0690700016</t>
+          <t>0630109758</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20260716</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0105567000055</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D17" t="n">
+        <v>765541000240</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>บริษัท สยาม การ์เมนท์ อิมปอร์ต จำกัด</t>
+          <t>บริษัท แลนโจ เอ็นเตอร์ไพรส์(ประเทศไทย)จำกัด</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Siam Garment Import Co., Ltd.</t>
+          <t>LANJO ENTERPRISES(THAILAND)CO.,LTD</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6109100010</v>
+        <v>39191010</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>50500</v>
+        <v>45545.22</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>MEN'S COTTON T-SHIRT ROUND NECK LONG SLEEVE</t>
+          <t>DOUBLE SIDE ADHESIVE TAPE</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>เสื้อยืดคอกลมแขนยาวผู้ชาย ผ้าฝ้าย</t>
+          <t>เทปสองหน้า (รายละเอียดตามอินวอยซ์แนบ)</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>175</v>
+        <v>66</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1642,71 +1590,67 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2900</v>
+        <v>66</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>KGM</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0690700017</t>
+          <t>0630109758</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20260717</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0105567000055</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>00000</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D18" t="n">
+        <v>765541000240</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>บริษัท สยาม การ์เมนท์ อิมปอร์ต จำกัด</t>
+          <t>บริษัท แลนโจ เอ็นเตอร์ไพรส์(ประเทศไทย)จำกัด</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Siam Garment Import Co., Ltd.</t>
+          <t>LANJO ENTERPRISES(THAILAND)CO.,LTD</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6109100010</v>
+        <v>39100020</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2100</v>
+        <v>11202.65</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>MEN'S COTTON T-SHIRT ROUND NECK</t>
+          <t>SILICONE RUBBER</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>เสื้อยืดคอกลมผู้ชาย ผ้าฝ้าย</t>
+          <t>ยางซิลิโคน (รายละเอียดตามอินวอยซ์แนบ)</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1714,71 +1658,67 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2850</v>
+        <v>17</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>KGM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0690700018</t>
+          <t>0630109765</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20260718</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0105569000066</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>00002</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100551000898</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>บริษัท แฟชั่น เทรดดิ้ง จำกัด</t>
+          <t>มารูเบนิ-อีโตชู สตีล พีทีอี ลิมิเต็ด สาขากรุงเทพฯ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fashion Trading Co., Ltd.</t>
+          <t>MARUBENI-ITOCHU STEEL PTE LTD BANGKOK BRANCH</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6109100090</v>
+        <v>72112390</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>61000</v>
+        <v>104604.48</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>WOMEN'S COTTON T-SHIRT V-NECK</t>
+          <t>COLD ROLLED STEEL SHEET IN COIL(SOFT MAGNETIC IRON PLATE JIS C 2504) NUSPO-SB SIZE : 0.8X185XC</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>เสื้อยืดคอวีผู้หญิง ผ้าฝ้าย</t>
+          <t>ผลิตภัณฑ์แผ่นรีดทำด้วยเหล็กหรือเหล็กกล้าไม่เจือ มีความกว้างน้อยกว่า 600มม. ผ่านการอบอ่อน มีคาร์บอนน้อยกว่า 0.01%(การยกเว้นอากรและลดอัตราอากรสำหรับของที่มีถิ่นกำเนิดจากญี่ปุ่น)</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>150</v>
+        <v>1497</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1786,71 +1726,67 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2500</v>
+        <v>1.497</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>TNE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0690700019</t>
+          <t>0630111050</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20260719</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0105569000066</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>00002</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D20" t="n">
+        <v>115545010385</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>บริษัท แฟชั่น เทรดดิ้ง จำกัด</t>
+          <t>บริษัท วินแชนซ์ อินดัสตรีส์ จำกัด</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fashion Trading Co., Ltd.</t>
+          <t>WIN CHANCE INDUSTRIES CO.,LTD.</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6109100090</v>
+        <v>39172100</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>VN</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>59800</v>
+        <v>6726.33</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>WOMEN'S COTTON T-SHIRT V-NECK SLIM FIT</t>
+          <t>MARKER TUBE MARKER TUBE MODEL 3.0 70M/ROLL,MARKER TUBE MODEL 3.2 64M/ROLL,MARKER TUBE MODEL 3.6 58M/ROLL,MARKER TUBE MODEL 4.2 50M/ROLL,MARKER TUBE MODEL 5.1 40M/ROLL,MARKER TUBE MODEL 6.2 30M/ROLL</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>เสื้อยืดคอวีทรงสลิมผู้หญิง ผ้าฝ้าย</t>
+          <t>ปลอกมาร์กเกอร์ (รายละเอียดตามINV.แนบ)</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>148</v>
+        <v>71.5</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1858,50 +1794,46 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>2450</v>
+        <v>90</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>RO</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0690700020</t>
+          <t>0630111050</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20260720</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>0105569000066</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>00002</t>
-        </is>
+        <v>20200110</v>
+      </c>
+      <c r="D21" t="n">
+        <v>115545010385</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>บริษัท แฟชั่น เทรดดิ้ง จำกัด</t>
+          <t>บริษัท วินแชนซ์ อินดัสตรีส์ จำกัด</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fashion Trading Co., Ltd.</t>
+          <t>WIN CHANCE INDUSTRIES CO.,LTD.</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6109100090</v>
+        <v>39173129</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1909,20 +1841,20 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>60500</v>
+        <v>32683.77</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>WOMEN'S COTTON T-SHIRT CREW NECK</t>
+          <t>PA CORRUGATED PIPE AD13,PA CORRUGATED PIPE AD15.8,PA CORRUGATED PIPE AD21.2</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>เสื้อยืดคอกลมผู้หญิง ผ้าฝ้าย</t>
+          <t>ท่ออ่อน (รายละเอียดINV.แนบ)</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>152</v>
+        <v>104.14</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1930,11 +1862,5451 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>2550</v>
+        <v>4000</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>MTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0630111050</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D22" t="n">
+        <v>115545010385</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>บริษัท วินแชนซ์ อินดัสตรีส์ จำกัด</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>WIN CHANCE INDUSTRIES CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>39173129</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>142080.53</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>PP CORRUGATED PIPE AD10(300M/ROLL),PP CORRUGATED PIPE AD13(100M/ROLL),PP CORRUGATED PIPE AD21.2(100M/ROLL),PP CORRUGATED PIPE AD28.5(50M/ROLL),PP CORRUGATED PIPE AD42.2(50M/ROLL),PP CORRUGATED PIPE AD 54.5(25M/ROLL),PP OPEN CORRUGATED PIPE AD13(100M/ROLL),PP OPEN CORRUGATED PIPE AD15.8(100M/ROLL),PP OPEN CORRUGATED PIPE AD21.2(100M/ROLL),PP OPEN CORRUGATED PIPE AD28.5(50M/ROLL),PP OPEN CORRUGATED PIPE AD34.5(50M/ROLL),PP OPEN CORRUGATED PIPE AD42.5(50M/ROLL),PP OPEN CORRUGATED PIPE AD54.5(25M/ROLL),</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ท่ออ่อน (รายละเอียดINV.แนบ)</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1133.85</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>340</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0630111070</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D23" t="n">
+        <v>105534045671</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>บริษัท ไทยมิตซุยสเปเชียลตี้เคมีคอล จำกัด</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>THAI MITSUI SPECIALTY CHEMICALS CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>39072090</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1888476.74</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>POLYPROPYLENE GLYCOL Y-7310</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>โพลีโพรไพลีนไกลคอล</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>33600</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0630111166</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D24" t="n">
+        <v>105531040228</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>บริษัท ไซโก พรีซีชั่น (ประเทศไทย) จำกัด</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SEIKO PRECISION (THAILAND) CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>39079990</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>32625.43</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>PLASTIC MAGNET RESIN</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>เม็ดพลาสติกใช้สำหรับหล่อหลอม</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>200</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>200000</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>GRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0630107645</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D25" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>72272000</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>49883.21</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  9254 13.00MM</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนขดมาเป็นม้วนทำด้วยเหล็กกล้าซิลิโคแมงกานีส</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>2038</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>2.038</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0630107645</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D26" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>72272000</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>251521.03</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  9254 15.00MM</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนขดมาเป็นม้วนทำด้วยเหล็กกล้าซิลิโคแมงกานีส</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>10276</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>10.276</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0630107645</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D27" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>72272000</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>5144677.09</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  9254 15.50MM</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนขดมาเป็นม้วนทำด้วยเหล็กกล้าซิลิโคแมงกานีส</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>210188</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>210.188</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0630107645</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D28" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>72272000</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>2631767.61</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  9254 19.00MM</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนขดมาเป็นม้วนทำด้วยเหล็กกล้าซิลิโคแมงกานีส</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>107522</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>107.522</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0630107645</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D29" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>72272000</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>265435.74</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  ACROS1950 12.70MM</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนขดมาเป็นม้วนทำด้วยเหล็กกล้าซิลิโคแมงกานีส</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>8152</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>8.151999999999999</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0630107645</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D30" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>72272000</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>648155.27</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  ACROS1950 12.00MM</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนขดมาเป็นม้วนทำด้วยเหล็กกล้าซิลิโคแมงกานีส</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>19906</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>19.906</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0630107645</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D31" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>72279000</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>209249.33</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  UHS1900M JIS G4801 12.00MM</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนขดมาเป็นม้วนทำด้วยเหล็กกล้าเจือ</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>5918</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>5.918</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0630107645</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D32" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>205919.96</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE ROD FOR MANUFACTURING COLD DRAWN BAR.  S35C JIS G4051 22.00MM</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>6446</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>6.446</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0630107656</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D33" t="n">
+        <v>255540000097</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>บริษัท เอชจีเอสที (ประเทศไทย) จำกัด</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>HGST (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>73269099</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>56948.45</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>R1X72 KAZU CROSS ROLLER BEARING</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>รองลื่น</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>200</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D34" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>39241090</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>10756.36</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RICE SCOOP N225</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ทัพพี</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>124.3</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1980</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D35" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>73049090</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>28003.59</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>SHOWER HOSE 1.5M</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>สายฝักบัว</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>184</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>864</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D36" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>22496.45</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>TOOTHPICK 2017#</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>ไม้จิ้มฟัน</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>2240</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D37" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>39241090</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>7669.35</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>CHOPSTICKS 1980#</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>ตะเกียบ</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>112</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D38" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>7395.32</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>TOOTHPICK 1812#</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ไม้จิ้มฟัน</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>1080</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D39" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>39241090</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>16361.03</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>CHOP BOARD 6220#</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>ตะเกียบ</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>224</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>640</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D40" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>8239</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>BIRD SWING PJ-236B</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>ของเล่นสัตว์เลี้ยง</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>32</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>480</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D41" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>5971.06</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>BIRD STANDING POLE PJ-194</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>คอนนกเกาะ</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>240</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D42" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>8162.44</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>BIRD FEEDER YSQN-120</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ภาชนะใส่อาหารสัตว์เลี้ยง</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>55</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D43" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>39241090</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>56880.03</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>KIDS SPOON SET S-4#</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>ช้อน</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D44" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>25164.8</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>TONGKAT 4 STND</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>ไม้ค้ำยัน</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>140</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>175</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D45" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>25390.53</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>CRUTCH DT-608#</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>ไม้ค้ำยัน</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>540</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D46" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>15064.67</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>CRUTCH DT-9126</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>ไม้ค้ำยัน</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>90</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>300</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D47" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>12051.8</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>TREKKING POLE DT-366</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ไม้ค้ำยัน</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>240</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D48" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>9860.42</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>CRUTCH DT-9719</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>ไม้ค้ำยัน</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>180</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D49" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>73219090</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>9255.24</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>G.STAND BLK-B</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>ส่วนประกอบเตา</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>199.95</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>930</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D50" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>39199099</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>10360.19</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>POM POM ART CR0357#</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>สติ๊กเกอร์</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>576</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D51" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>39261000</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>38126.81</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>DOCUMENT FILE FC 20P CYFC20AB#</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>แฟ้มใส่เอกสาร</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>471</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>2880</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D52" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>39261000</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>40263.5</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>INDEX DIVIDER A-Z IN4119#</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>แฟ้มใส่เอกสาร</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>516.6</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>2520</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0630107753</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D53" t="n">
+        <v>205560011329</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>บริษัท เคทีเอ็น อิมปอร์ต เอ็กซ์ปอร์ต เเอนด์ ชิปปิ้ง จำกัด</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>KTN IMPORT EXPORT &amp; SHIPPING CO.,LTD</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>39261000</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>48381.58</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>DOCUMENT FILE FC 40P CYFC40AB#</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>แฟ้มใส่เอกสาร</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>544.8</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>2304</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D54" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>18276.85</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>BEZEL SCANNER-PREMIUM</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>468.581</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>1721</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D55" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>BEZEL SCANNER-PREMIUM</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>10.619</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>39</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D56" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>2871.04</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>COVER REAR</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>800</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D57" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1343.86</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ASSY BASE SCANNER PREMIUM</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>37</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D58" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>10460.3</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ASSY BASE SCANNER PREMIUM</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>192</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>288</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D59" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>9629.93</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>CLEANOUT BODY</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>228.6</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>2160</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D60" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>6900.6</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>PLATE-GEAR_LT_TRANNY</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>6000</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D61" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>8032</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>WALL-DOUBLE SEPARATOR</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>1053.68</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>2520</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D62" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>17770.18</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>TRANS-HOUSING TUBE-PUMP</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>169.722</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>2651</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D63" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1526.47</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>TRANS-HOUSING TUBE-PUMP</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>14.661</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>229</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D64" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>6929.2</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>COVER-RIGHT</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>51.217</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>800</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D65" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>1553.45</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ADF COVER TRIM</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>71</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>A630100147</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D66" t="n">
+        <v>107543000023</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>บริษัท แคล-คอมพ์ อีเล็กโทรนิคส์(ประเทศไทย) จำกัด (มหาชน)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CAL-COMP ELECTRONICS  (THAILAND) PUBLIC COMPANY  LIMITED</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>2138.67</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>COVER FRONT</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>ชิ้นส่วนพลาสติกของเครื่องอิเล็กทรอนิกส์</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>340</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0630109965</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D67" t="n">
+        <v>245552000569</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>บริษัท จั๊มเวย์ จำกัด</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>JUMPWAY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>72091610</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>229327.49</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>STEEL SHEETS  2.000 MM x 1219 MM x COIL COLD ROLLED STEEL SHEET IN COIL JIS G3141 SPCC-SD</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>เหล็กแผ่นม้วนรีดเย็นมีความกว้าง มากกว่า 600 มิลลิเมตร (เหล็กกล้าไม่เจือ) การลดอัตราอากรและยกเว้นอากรศุลกากรตามมาตรา 12 แห่งพระราชกำหนดพิกัดอัตราศุลกากร พ.ศ. 2530</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>11105</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>11105</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0630109965</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D68" t="n">
+        <v>245552000569</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>บริษัท จั๊มเวย์ จำกัด</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>JUMPWAY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>72091710</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>446458.87</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>STEEL SHEETS  0.500 MM x 1219 MM x COIL COLD ROLLED STEEL SHEET IN COIL JIS G3141 SPCD-SD</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>เหล็กแผ่นม้วนรีดเย็นมีความกว้าง มากกว่า 600 มิลลิเมตร (เหล็กกล้าไม่เจือ) การลดอัตราอากรและยกเว้นอากรศุลกากรตามมาตรา 12 แห่งพระราชกำหนดพิกัดอัตราศุลกากร พ.ศ. 2530</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>20905</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>20905</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0630109965</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D69" t="n">
+        <v>245552000569</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>บริษัท จั๊มเวย์ จำกัด</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>JUMPWAY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>72091610</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>658793.71</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>STEEL SHEETS  2.000 MM x 1219 MM x COIL COLD ROLLED STEEL SHEET IN COIL JIS G3141 SPCC-SD</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>เหล็กแผ่นม้วนรีดเย็นมีความกว้าง มากกว่า 600 มิลลิเมตร (เหล็กกล้าไม่เจือ) การลดอัตราอากรและยกเว้นอากรศุลกากรตามมาตรา 12 แห่งพระราชกำหนดพิกัดอัตราศุลกากร พ.ศ. 2530</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>33390</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>33390</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0630109965</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D70" t="n">
+        <v>245552000569</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>บริษัท จั๊มเวย์ จำกัด</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>JUMPWAY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>72082600</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>778831.38</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>STEEL SHEETS 4.000MMx1109MMxCOIL HOT ROLLED STEEL SHEET IN COIL  JIS G3131 SPHC P-O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>เหล็กแผ่นม้วนรีดร้อนมีความกว้าง มากกว่า 600 มิลลิเมตรผ่านการกัดล้างแล้ว (เหล็กกล้าไม่เจือ) การลดอัตราอากรและยกเว้นอากรศุลกากรตามมาตรา 12 แห่งพระราชกำหนดพิกัดอัตราศุลกากร พ.ศ. 2530</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>38810</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>38810</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0630109965</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D71" t="n">
+        <v>245552000569</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>บริษัท จั๊มเวย์ จำกัด</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>JUMPWAY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>72082600</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>355501.19</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>STEEL SHEETS 4.000MMx1109MMxCOIL HOT ROLLED STEEL SHEET IN COIL  JIS G3131 SPHC P-O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>เหล็กแผ่นม้วนรีดร้อนมีความกว้าง มากกว่า 600 มิลลิเมตรผ่านการกัดล้างแล้ว (เหล็กกล้าไม่เจือ) การลดอัตราอากรและยกเว้นอากรศุลกากรตามมาตรา 12 แห่งพระราชกำหนดพิกัดอัตราศุลกากร พ.ศ. 2530</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>17715</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>17715</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0630109965</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D72" t="n">
+        <v>245552000569</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>บริษัท จั๊มเวย์ จำกัด</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>JUMPWAY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>72104912</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>160249.22</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>GALVANIZED STEEL SHEET  0.800MMx1260MMXCOIL HOT DIP GALVANIZED STEEL SHEET IN COIL JIS G3302 SGCC</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>ผลิตภํณฑ์แผ่นรีดทำด้วยเหล็กมีความกว้างมากกว่า 600 มิลลิเมตรเตลือบด้วยกาวาไนซ์ (ตามเอกสารแนบ) การลดอัตราอากรและยกเว้นอากรศุลกากรตามมาตรา 12 แห่งพระราชกำหนดพิกัดอัตราศุลกากร พ.ศ. 2530</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>7010</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>7010</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0630109965</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D73" t="n">
+        <v>245552000569</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>บริษัท จั๊มเวย์ จำกัด</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>JUMPWAY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>72104912</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>505452.5</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>GALVANIZED STEEL SHEET  1.000MMx1219MMXCOIL HOT DIP GALVANIZED STEEL SHEET IN COIL JIS G3302 SGCC</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>ผลิตภํณฑ์แผ่นรีดทำด้วยเหล็กมีความกว้างมากกว่า 600 มิลลิเมตรเตลือบด้วยกาวาไนซ์ (ตามเอกสารแนบ) การลดอัตราอากรและยกเว้นอากรศุลกากรตามมาตรา 12 แห่งพระราชกำหนดพิกัดอัตราศุลกากร พ.ศ. 2530</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>22565</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>22565</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0630111178</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D74" t="n">
+        <v>105537006439</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>บริษัท แคนนอน มาร์เก็ตติ้ง(ไทยแลนด์) จำกัด</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>CANON MARKETING (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>205.27</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>COLLAR</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>ปลอกพลาสติก</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>10</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0630111178</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D75" t="n">
+        <v>105537006439</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>บริษัท แคนนอน มาร์เก็ตติ้ง(ไทยแลนด์) จำกัด</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>CANON MARKETING (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>39269099</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>6024.8</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>BARREL ASS'Y GROUP 6</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>กระบอกเลนส์ทำจากพลาสติก</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0630111216</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D76" t="n">
+        <v>105534021577</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>บริษัท นิทซู โลจิสติกส์ (ประเทศไทย) จำกัด</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>NITTSU LOGISTICS (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>73269099</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>40139.25</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>THRUST BUSH (No commercial value)</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>ส่วนประกอบมอเตอร์ทำด้วยสแตนเลส</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>36000</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D77" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>72139190</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>70454.42</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  SGD1 JIS G3108 7.00MM</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมน้อยกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D78" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>72139190</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>73519.16</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS S20C JIS G4051 9.00MM</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมน้อยกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>2111</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D79" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>67668.28999999999</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S33C JIS G4051 23.00MM</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>1943</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>1.943</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D80" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>1300635.47</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S35C JIS G4051 18.00MM</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>37346</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>37.346</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D81" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>180178.74</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S35CD JIS G4051 22.00MM</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>5040</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D82" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>425314.88</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S35CD JIS G4051 24.00MM</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>11897</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>11.897</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D83" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>711098.33</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S35CD JIS G4051 26.00MM</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>19891</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>19.891</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D84" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>72139190</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>87410.66</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  ELCH2 12.50MM</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมน้อยกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>2016</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D85" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>352027.34</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  ELCH2 26.00MM</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>8119</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>8.119</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D86" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>2251084.53</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  ELCH2 35.00MM</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>51918</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>51.918</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D87" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>213661.54</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  SGDB JIS G3108 16.00MM</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>6135</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>6.135</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D88" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>133351.32</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S15C JIS G4051 16.00MM</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>3829</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>3.829</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D89" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>72279000</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>74644.25</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS   SCR420H  JIS G4052 23.00MM</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนขดมาเป็นม้วนทำด้วยเหล็กกล้าเจือ</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>2020</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D90" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>73902.12</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  SGDB JIS G3108 16.00MM</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>2122</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>2.122</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D91" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>67076.10000000001</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S15C JIS G4051 16.00MM</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>1.926</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D92" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>62339.67</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  SGDB JIS G3108 21.00MM</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>1790</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D93" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>70419.45</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  SGDB JIS G3108 22.00MM</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>2022</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D94" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>73275.24000000001</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS S15C JIS G4051 22.00MM</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>2104</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D95" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>426765.57</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S35C JIS G4051 18.00MM</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>12254</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>12.254</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D96" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>70489.11</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S35C JIS G4051 20.00MM</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D97" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>72714.92999999999</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  S35CD JIS G4051 22.00MM</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>2034</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>2.034</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D98" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>90319.03</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  ELCH2S 16.00MM</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>1998</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>1.998</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D99" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>87237.22</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  ELCH2 16.00MM</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14 มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>2012</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D100" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>211745.93</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS  SGDB JIS G3108 22.00MM</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>6080</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>TNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>A010</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0630107636</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>20200110</v>
+      </c>
+      <c r="D101" t="n">
+        <v>105539032194</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>บริษัท มหาจักร เกียวโด จำกัด</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>MAHAJAK KYODO CO., LTD.</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>72139990</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>512160.48</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>HOT ROLLED STEEL WIRE RODS S15C JIS G4051 20.00MM</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>เหล็กเส้นรีดร้อนไม่มีธาตุคาร์บอนสูง ภาคตัดขวางเป็นวงกลมมากกว่า 14มม.เหล็กไม่เจือ</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>14706</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>KGM</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>14.706</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>TNE</t>
         </is>
       </c>
     </row>
